--- a/docs/102_RIME對照工具【方音符號】.xlsx
+++ b/docs/102_RIME對照工具【方音符號】.xlsx
@@ -8,25 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F0A806-10D6-49BB-80E3-17F8F4797D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E587D86A-1CA9-426E-ABF9-3D9D5A92C6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{F24D58E0-B204-45A4-8E74-84AA1A2ACD5E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{F24D58E0-B204-45A4-8E74-84AA1A2ACD5E}"/>
   </bookViews>
   <sheets>
     <sheet name="【韻】韻母清單" sheetId="1" r:id="rId1"/>
     <sheet name="【韻】韻母清單 (台語注音符號)" sheetId="7" r:id="rId2"/>
-    <sheet name="【韻】韻母清單(倒排序)" sheetId="2" r:id="rId3"/>
-    <sheet name="【聲】聲母對照表（注音二式）" sheetId="4" r:id="rId4"/>
-    <sheet name="【聲】聲母對照表 (台語注音)" sheetId="5" r:id="rId5"/>
-    <sheet name="【韻】韻母清單（白話字）" sheetId="6" r:id="rId6"/>
-    <sheet name="【韻】韻母清單（拼音字母標聲調）" sheetId="3" r:id="rId7"/>
+    <sheet name="【韻】韻母清單 (台語注音二式)" sheetId="8" r:id="rId3"/>
+    <sheet name="【韻】韻母清單(倒排序)" sheetId="2" r:id="rId4"/>
+    <sheet name="【聲】聲母對照表（注音二式）" sheetId="4" r:id="rId5"/>
+    <sheet name="【聲】聲母對照表 (台語注音)" sheetId="5" r:id="rId6"/>
+    <sheet name="【韻】韻母清單（白話字）" sheetId="6" r:id="rId7"/>
+    <sheet name="【韻】韻母清單（拼音字母標聲調）" sheetId="3" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">【韻】韻母清單!$B$3:$N$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'【韻】韻母清單 (台語注音二式)'!$B$3:$O$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'【韻】韻母清單 (台語注音符號)'!$B$3:$N$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'【韻】韻母清單（白話字）'!$B$3:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'【韻】韻母清單（拼音字母標聲調）'!$B$3:$L$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'【韻】韻母清單(倒排序)'!$B$3:$L$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'【韻】韻母清單（白話字）'!$B$3:$L$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'【韻】韻母清單（拼音字母標聲調）'!$B$3:$L$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'【韻】韻母清單(倒排序)'!$B$3:$L$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4523" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5483" uniqueCount="652">
   <si>
     <t>響度優先次第： a &gt; oo &gt; (e = o) &gt; (i = u)〈低元音 &gt; 高元音 &gt; 無擦通音 &gt; 擦音 &gt; 塞音〉</t>
   </si>
@@ -2096,6 +2098,69 @@
   </si>
   <si>
     <t>台語注音</t>
+  </si>
+  <si>
+    <t>L台語注音二式</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Luaih</t>
+  </si>
+  <si>
+    <t>Liah</t>
+  </si>
+  <si>
+    <t>Liau</t>
+  </si>
+  <si>
+    <t>Liuh</t>
+  </si>
+  <si>
+    <t>Luai</t>
+  </si>
+  <si>
+    <t>Lah</t>
+  </si>
+  <si>
+    <t>Lai</t>
+  </si>
+  <si>
+    <t>Leh</t>
+  </si>
+  <si>
+    <t>Lia</t>
+  </si>
+  <si>
+    <t>Lio</t>
+  </si>
+  <si>
+    <t>Liu</t>
+  </si>
+  <si>
+    <t>Loh</t>
+  </si>
+  <si>
+    <t>Lua</t>
+  </si>
+  <si>
+    <t>Lui</t>
+  </si>
+  <si>
+    <t>La</t>
+  </si>
+  <si>
+    <t>Le</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>Loo</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>iek</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -14987,6 +15052,6245 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB6919F-B20D-4595-A34F-E98D5384E4FC}">
+  <dimension ref="A1:AV97"/>
+  <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="8.375" style="2" customWidth="1"/>
+    <col min="2" max="5" width="15.375" style="2" customWidth="1"/>
+    <col min="6" max="10" width="15.375" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="13" width="15.375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.125" style="52" customWidth="1"/>
+    <col min="17" max="17" width="15.125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="2.875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="15.5" style="3" customWidth="1"/>
+    <col min="20" max="20" width="16.75" style="3" customWidth="1"/>
+    <col min="21" max="21" width="4.5" style="2" customWidth="1"/>
+    <col min="22" max="22" width="51.75" style="6" customWidth="1"/>
+    <col min="23" max="23" width="9" style="2"/>
+    <col min="24" max="35" width="7.5" style="7" customWidth="1"/>
+    <col min="36" max="41" width="19.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="42" max="44" width="19.875" style="8" customWidth="1"/>
+    <col min="45" max="45" width="19.875" style="2" customWidth="1"/>
+    <col min="46" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:48" ht="46.5" customHeight="1">
+      <c r="A1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:48" ht="27" thickBot="1">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="V2" s="10"/>
+      <c r="Y2" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="7">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>4</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="7">
+        <v>6</v>
+      </c>
+      <c r="AE2" s="7">
+        <v>7</v>
+      </c>
+      <c r="AF2" s="7">
+        <v>8</v>
+      </c>
+      <c r="AG2" s="7">
+        <v>9</v>
+      </c>
+      <c r="AH2" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="13"/>
+      <c r="P3" s="51" t="str">
+        <f>G3</f>
+        <v>L台語注音二式</v>
+      </c>
+      <c r="Q3" s="11" t="str">
+        <f>K3</f>
+        <v>方音符號</v>
+      </c>
+      <c r="S3" s="11" t="str">
+        <f>P3</f>
+        <v>L台語注音二式</v>
+      </c>
+      <c r="T3" s="11" t="str">
+        <f>K3</f>
+        <v>方音符號</v>
+      </c>
+      <c r="V3" s="14"/>
+      <c r="X3" s="16"/>
+      <c r="Z3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF3" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH3" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI3" s="18"/>
+    </row>
+    <row r="4" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A4" s="19">
+        <v>73</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>633</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>359</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>573</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="23">
+        <f t="shared" ref="N4:N67" si="0" xml:space="preserve"> LEN(C4)</f>
+        <v>6</v>
+      </c>
+      <c r="O4" s="24"/>
+      <c r="P4" s="51" t="str">
+        <f t="shared" ref="P4:P67" si="1">G4</f>
+        <v>Luaih</v>
+      </c>
+      <c r="Q4" s="51" t="str">
+        <f t="shared" ref="Q4:Q67" si="2">K4</f>
+        <v>ㄨㆮㆷ</v>
+      </c>
+      <c r="S4" s="3" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(P4)</f>
+        <v>Luaih</v>
+      </c>
+      <c r="T4" s="3" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT(Q4, ""), "" )</f>
+        <v>ㄨㆮㆷ</v>
+      </c>
+      <c r="U4" s="25"/>
+      <c r="V4" s="26" t="str">
+        <f xml:space="preserve"> IF(AND(Q4&lt;&gt;"", P4&lt;&gt;""), "    - xform/》" &amp; S4 &amp;  "/"  &amp; T4 &amp;  "》/", "")</f>
+        <v xml:space="preserve">    - xform/》Luaih/ㄨㆮㆷ》/</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="27" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT($X4, IF(Y$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(Y$3,4)))))</f>
+        <v>a</v>
+      </c>
+      <c r="Z4" s="27" t="str">
+        <f t="shared" ref="Z4:AH4" si="3" xml:space="preserve"> _xlfn.CONCAT($X4, IF(Z$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(Z$3,4)))))</f>
+        <v>á</v>
+      </c>
+      <c r="AA4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>à</v>
+      </c>
+      <c r="AB4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>a</v>
+      </c>
+      <c r="AC4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>ǎ</v>
+      </c>
+      <c r="AD4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>á</v>
+      </c>
+      <c r="AE4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>ā</v>
+      </c>
+      <c r="AF4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>a̍</v>
+      </c>
+      <c r="AG4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>a̋</v>
+      </c>
+      <c r="AH4" s="27" t="str">
+        <f t="shared" si="3"/>
+        <v>å</v>
+      </c>
+      <c r="AJ4" s="28" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, Y$2, "/", Y4, "/")</f>
+        <v xml:space="preserve">    - xform/》a1/a/</v>
+      </c>
+      <c r="AK4" s="28" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, Z$2, "/", Z4, "/")</f>
+        <v xml:space="preserve">    - xform/》a2/á/</v>
+      </c>
+      <c r="AL4" s="28" t="str">
+        <f t="shared" ref="AL4:AQ10" si="4" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AA$2, "/", AA4, "/")</f>
+        <v xml:space="preserve">    - xform/》a3/à/</v>
+      </c>
+      <c r="AM4" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》a4/a/</v>
+      </c>
+      <c r="AN4" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》a5/ǎ/</v>
+      </c>
+      <c r="AO4" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》a6/á/</v>
+      </c>
+      <c r="AP4" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》a7/ā/</v>
+      </c>
+      <c r="AQ4" s="28" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AF$2, "/", AF4, "/")</f>
+        <v xml:space="preserve">    - xform/》a8/a̍/</v>
+      </c>
+      <c r="AR4" s="28" t="str">
+        <f t="shared" ref="AR4:AS10" si="5" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X4, AG$2, "/", AG4, "/")</f>
+        <v xml:space="preserve">    - xform/》a9/a̋/</v>
+      </c>
+      <c r="AS4" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》a9/å/</v>
+      </c>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="7"/>
+    </row>
+    <row r="5" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A5" s="19">
+        <v>32</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>634</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="M5" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="23">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O5" s="24"/>
+      <c r="P5" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Liah</v>
+      </c>
+      <c r="Q5" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆩㆷ</v>
+      </c>
+      <c r="S5" s="3" t="str">
+        <f t="shared" ref="S5:S68" si="6" xml:space="preserve"> _xlfn.CONCAT(P5)</f>
+        <v>Liah</v>
+      </c>
+      <c r="T5" s="3" t="str">
+        <f t="shared" ref="T5:T68" si="7" xml:space="preserve"> IFERROR( _xlfn.CONCAT(Q5, ""), "" )</f>
+        <v>ㄧㆩㆷ</v>
+      </c>
+      <c r="U5" s="25"/>
+      <c r="V5" s="26" t="str">
+        <f t="shared" ref="V5:V68" si="8" xml:space="preserve"> IF(AND(Q5&lt;&gt;"", P5&lt;&gt;""), "    - xform/》" &amp; S5 &amp;  "/"  &amp; T5 &amp;  "》/", "")</f>
+        <v xml:space="preserve">    - xform/》Liah/ㄧㆩㆷ》/</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y5" s="27" t="str">
+        <f t="shared" ref="Y5:AH10" si="9" xml:space="preserve"> _xlfn.CONCAT($X5, IF(Y$3="", "", _xlfn.UNICHAR( HEX2DEC( RIGHT(Y$3,4)))))</f>
+        <v>i</v>
+      </c>
+      <c r="Z5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>í</v>
+      </c>
+      <c r="AA5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ì</v>
+      </c>
+      <c r="AB5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>i</v>
+      </c>
+      <c r="AC5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ǐ</v>
+      </c>
+      <c r="AD5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>í</v>
+      </c>
+      <c r="AE5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ī</v>
+      </c>
+      <c r="AF5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>i̍</v>
+      </c>
+      <c r="AG5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>i̋</v>
+      </c>
+      <c r="AH5" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>i̊</v>
+      </c>
+      <c r="AJ5" s="28" t="str">
+        <f t="shared" ref="AJ5:AK10" si="10" xml:space="preserve"> _xlfn.CONCAT("    - xform/》", $X5, Y$2, "/", Y5, "/")</f>
+        <v xml:space="preserve">    - xform/》i1/i/</v>
+      </c>
+      <c r="AK5" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》i2/í/</v>
+      </c>
+      <c r="AL5" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》i3/ì/</v>
+      </c>
+      <c r="AM5" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》i4/i/</v>
+      </c>
+      <c r="AN5" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》i5/ǐ/</v>
+      </c>
+      <c r="AO5" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》i6/í/</v>
+      </c>
+      <c r="AP5" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》i7/ī/</v>
+      </c>
+      <c r="AQ5" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》i8/i̍/</v>
+      </c>
+      <c r="AR5" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》i9/i̋/</v>
+      </c>
+      <c r="AS5" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》i9/i̊/</v>
+      </c>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="7"/>
+    </row>
+    <row r="6" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A6" s="19">
+        <v>40</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="23">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O6" s="24"/>
+      <c r="P6" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Liau</v>
+      </c>
+      <c r="Q6" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆯ</v>
+      </c>
+      <c r="S6" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Liau</v>
+      </c>
+      <c r="T6" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆯ</v>
+      </c>
+      <c r="U6" s="25"/>
+      <c r="V6" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Liau/ㄧㆯ》/</v>
+      </c>
+      <c r="X6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>u</v>
+      </c>
+      <c r="Z6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ú</v>
+      </c>
+      <c r="AA6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ù</v>
+      </c>
+      <c r="AB6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>u</v>
+      </c>
+      <c r="AC6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ǔ</v>
+      </c>
+      <c r="AD6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ú</v>
+      </c>
+      <c r="AE6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ū</v>
+      </c>
+      <c r="AF6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>u̍</v>
+      </c>
+      <c r="AG6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ű</v>
+      </c>
+      <c r="AH6" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ů</v>
+      </c>
+      <c r="AJ6" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》u1/u/</v>
+      </c>
+      <c r="AK6" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》u2/ú/</v>
+      </c>
+      <c r="AL6" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》u3/ù/</v>
+      </c>
+      <c r="AM6" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》u4/u/</v>
+      </c>
+      <c r="AN6" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》u5/ǔ/</v>
+      </c>
+      <c r="AO6" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》u6/ú/</v>
+      </c>
+      <c r="AP6" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》u7/ū/</v>
+      </c>
+      <c r="AQ6" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》u8/u̍/</v>
+      </c>
+      <c r="AR6" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》u9/ű/</v>
+      </c>
+      <c r="AS6" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》u9/ů/</v>
+      </c>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="7"/>
+    </row>
+    <row r="7" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A7" s="19">
+        <v>49</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>245</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="K7" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="23">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O7" s="24"/>
+      <c r="P7" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Liuh</v>
+      </c>
+      <c r="Q7" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆫㆷ</v>
+      </c>
+      <c r="S7" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Liuh</v>
+      </c>
+      <c r="T7" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆫㆷ</v>
+      </c>
+      <c r="U7" s="25"/>
+      <c r="V7" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Liuh/ㄧㆫㆷ》/</v>
+      </c>
+      <c r="X7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>e</v>
+      </c>
+      <c r="Z7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>é</v>
+      </c>
+      <c r="AA7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>è</v>
+      </c>
+      <c r="AB7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>e</v>
+      </c>
+      <c r="AC7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ě</v>
+      </c>
+      <c r="AD7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>é</v>
+      </c>
+      <c r="AE7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ē</v>
+      </c>
+      <c r="AF7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>e̍</v>
+      </c>
+      <c r="AG7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>e̋</v>
+      </c>
+      <c r="AH7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>e̊</v>
+      </c>
+      <c r="AJ7" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》e1/e/</v>
+      </c>
+      <c r="AK7" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》e2/é/</v>
+      </c>
+      <c r="AL7" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》e3/è/</v>
+      </c>
+      <c r="AM7" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》e4/e/</v>
+      </c>
+      <c r="AN7" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》e5/ě/</v>
+      </c>
+      <c r="AO7" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》e6/é/</v>
+      </c>
+      <c r="AP7" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》e7/ē/</v>
+      </c>
+      <c r="AQ7" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》e8/e̍/</v>
+      </c>
+      <c r="AR7" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》e9/e̋/</v>
+      </c>
+      <c r="AS7" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》e9/e̊/</v>
+      </c>
+      <c r="AT7" s="27"/>
+      <c r="AU7" s="27"/>
+      <c r="AV7" s="7"/>
+    </row>
+    <row r="8" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A8" s="19">
+        <v>71</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>637</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="M8" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="23">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="O8" s="24"/>
+      <c r="P8" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Luai</v>
+      </c>
+      <c r="Q8" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㆮ</v>
+      </c>
+      <c r="S8" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Luai</v>
+      </c>
+      <c r="T8" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㆮ</v>
+      </c>
+      <c r="U8" s="25"/>
+      <c r="V8" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Luai/ㄨㆮ》/</v>
+      </c>
+      <c r="X8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>o</v>
+      </c>
+      <c r="Z8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ó</v>
+      </c>
+      <c r="AA8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ò</v>
+      </c>
+      <c r="AB8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>o</v>
+      </c>
+      <c r="AC8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ǒ</v>
+      </c>
+      <c r="AD8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ó</v>
+      </c>
+      <c r="AE8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ō</v>
+      </c>
+      <c r="AF8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>o̍</v>
+      </c>
+      <c r="AG8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ő</v>
+      </c>
+      <c r="AH8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>o̊</v>
+      </c>
+      <c r="AJ8" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》o1/o/</v>
+      </c>
+      <c r="AK8" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》o2/ó/</v>
+      </c>
+      <c r="AL8" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》o3/ò/</v>
+      </c>
+      <c r="AM8" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》o4/o/</v>
+      </c>
+      <c r="AN8" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》o5/ǒ/</v>
+      </c>
+      <c r="AO8" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》o6/ó/</v>
+      </c>
+      <c r="AP8" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》o7/ō/</v>
+      </c>
+      <c r="AQ8" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》o8/o̍/</v>
+      </c>
+      <c r="AR8" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》o9/ő/</v>
+      </c>
+      <c r="AS8" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》o9/o̊/</v>
+      </c>
+      <c r="AT8" s="27"/>
+      <c r="AU8" s="27"/>
+      <c r="AV8" s="7"/>
+    </row>
+    <row r="9" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A9" s="19">
+        <v>4</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O9" s="24"/>
+      <c r="P9" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Lah</v>
+      </c>
+      <c r="Q9" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆩㆷ</v>
+      </c>
+      <c r="S9" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Lah</v>
+      </c>
+      <c r="T9" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆩㆷ</v>
+      </c>
+      <c r="U9" s="25"/>
+      <c r="V9" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Lah/ㆩㆷ》/</v>
+      </c>
+      <c r="X9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m</v>
+      </c>
+      <c r="Z9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ḿ</v>
+      </c>
+      <c r="AA9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m̀</v>
+      </c>
+      <c r="AB9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m</v>
+      </c>
+      <c r="AC9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m̌</v>
+      </c>
+      <c r="AD9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ḿ</v>
+      </c>
+      <c r="AE9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m̄</v>
+      </c>
+      <c r="AF9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m̍</v>
+      </c>
+      <c r="AG9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m̋</v>
+      </c>
+      <c r="AH9" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>m̊</v>
+      </c>
+      <c r="AJ9" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》m1/m/</v>
+      </c>
+      <c r="AK9" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》m2/ḿ/</v>
+      </c>
+      <c r="AL9" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》m3/m̀/</v>
+      </c>
+      <c r="AM9" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》m4/m/</v>
+      </c>
+      <c r="AN9" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》m5/m̌/</v>
+      </c>
+      <c r="AO9" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》m6/ḿ/</v>
+      </c>
+      <c r="AP9" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》m7/m̄/</v>
+      </c>
+      <c r="AQ9" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》m8/m̍/</v>
+      </c>
+      <c r="AR9" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》m9/m̋/</v>
+      </c>
+      <c r="AS9" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》m9/m̊/</v>
+      </c>
+      <c r="AT9" s="27"/>
+      <c r="AU9" s="27"/>
+      <c r="AV9" s="7"/>
+    </row>
+    <row r="10" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A10" s="19">
+        <v>12</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>560</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="M10" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O10" s="24"/>
+      <c r="P10" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Lai</v>
+      </c>
+      <c r="Q10" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆮ</v>
+      </c>
+      <c r="S10" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Lai</v>
+      </c>
+      <c r="T10" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆮ</v>
+      </c>
+      <c r="U10" s="25"/>
+      <c r="V10" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Lai/ㆮ》/</v>
+      </c>
+      <c r="X10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>n</v>
+      </c>
+      <c r="Z10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ń</v>
+      </c>
+      <c r="AA10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ǹ</v>
+      </c>
+      <c r="AB10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>n</v>
+      </c>
+      <c r="AC10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ň</v>
+      </c>
+      <c r="AD10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>ń</v>
+      </c>
+      <c r="AE10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>n̄</v>
+      </c>
+      <c r="AF10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>n̍</v>
+      </c>
+      <c r="AG10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>n̋</v>
+      </c>
+      <c r="AH10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>n̊</v>
+      </c>
+      <c r="AJ10" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》n1/n/</v>
+      </c>
+      <c r="AK10" s="28" t="str">
+        <f t="shared" si="10"/>
+        <v xml:space="preserve">    - xform/》n2/ń/</v>
+      </c>
+      <c r="AL10" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》n3/ǹ/</v>
+      </c>
+      <c r="AM10" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》n4/n/</v>
+      </c>
+      <c r="AN10" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》n5/ň/</v>
+      </c>
+      <c r="AO10" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》n6/ń/</v>
+      </c>
+      <c r="AP10" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》n7/n̄/</v>
+      </c>
+      <c r="AQ10" s="28" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">    - xform/》n8/n̍/</v>
+      </c>
+      <c r="AR10" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》n9/n̋/</v>
+      </c>
+      <c r="AS10" s="28" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">    - xform/》n9/n̊/</v>
+      </c>
+      <c r="AT10" s="27"/>
+      <c r="AU10" s="27"/>
+      <c r="AV10" s="7"/>
+    </row>
+    <row r="11" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A11" s="19">
+        <v>19</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>640</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="M11" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O11" s="24"/>
+      <c r="P11" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Leh</v>
+      </c>
+      <c r="Q11" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆥㆷ</v>
+      </c>
+      <c r="S11" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Leh</v>
+      </c>
+      <c r="T11" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆥㆷ</v>
+      </c>
+      <c r="U11" s="25"/>
+      <c r="V11" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Leh/ㆥㆷ》/</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A12" s="19">
+        <v>30</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>562</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>641</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="M12" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O12" s="24"/>
+      <c r="P12" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Lia</v>
+      </c>
+      <c r="Q12" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆩ</v>
+      </c>
+      <c r="S12" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Lia</v>
+      </c>
+      <c r="T12" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆩ</v>
+      </c>
+      <c r="U12" s="25"/>
+      <c r="V12" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Lia/ㄧㆩ》/</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A13" s="19">
+        <v>43</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>563</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>642</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="M13" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O13" s="24"/>
+      <c r="P13" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Lio</v>
+      </c>
+      <c r="Q13" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆧ</v>
+      </c>
+      <c r="S13" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Lio</v>
+      </c>
+      <c r="T13" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆧ</v>
+      </c>
+      <c r="U13" s="25"/>
+      <c r="V13" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Lio/ㄧㆧ》/</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A14" s="19">
+        <v>48</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>564</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="M14" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O14" s="24"/>
+      <c r="P14" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Liu</v>
+      </c>
+      <c r="Q14" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆫ</v>
+      </c>
+      <c r="S14" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Liu</v>
+      </c>
+      <c r="T14" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆫ</v>
+      </c>
+      <c r="U14" s="25"/>
+      <c r="V14" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Liu/ㄧㆫ》/</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A15" s="19">
+        <v>55</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>644</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="M15" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O15" s="24"/>
+      <c r="P15" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Loh</v>
+      </c>
+      <c r="Q15" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆧㆷ</v>
+      </c>
+      <c r="S15" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Loh</v>
+      </c>
+      <c r="T15" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆧㆷ</v>
+      </c>
+      <c r="U15" s="25"/>
+      <c r="V15" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Loh/ㆧㆷ》/</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" ht="48.75" thickBot="1">
+      <c r="A16" s="19">
+        <v>65</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>569</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O16" s="24"/>
+      <c r="P16" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Lua</v>
+      </c>
+      <c r="Q16" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㆩ</v>
+      </c>
+      <c r="S16" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Lua</v>
+      </c>
+      <c r="T16" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㆩ</v>
+      </c>
+      <c r="U16" s="25"/>
+      <c r="V16" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Lua/ㄨㆩ》/</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A17" s="19">
+        <v>77</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>646</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="M17" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O17" s="24"/>
+      <c r="P17" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Lui</v>
+      </c>
+      <c r="Q17" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㆪ</v>
+      </c>
+      <c r="S17" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Lui</v>
+      </c>
+      <c r="T17" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㆪ</v>
+      </c>
+      <c r="U17" s="25"/>
+      <c r="V17" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Lui/ㄨㆪ》/</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A18" s="19">
+        <v>2</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>592</v>
+      </c>
+      <c r="M18" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O18" s="24"/>
+      <c r="P18" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>La</v>
+      </c>
+      <c r="Q18" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆩ</v>
+      </c>
+      <c r="S18" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>La</v>
+      </c>
+      <c r="T18" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆩ</v>
+      </c>
+      <c r="U18" s="25"/>
+      <c r="V18" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》La/ㆩ》/</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A19" s="19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>648</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="M19" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O19" s="24"/>
+      <c r="P19" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Le</v>
+      </c>
+      <c r="Q19" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆥ</v>
+      </c>
+      <c r="S19" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Le</v>
+      </c>
+      <c r="T19" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆥ</v>
+      </c>
+      <c r="U19" s="25"/>
+      <c r="V19" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Le/ㆥ》/</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A20" s="19">
+        <v>21</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>568</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="M20" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O20" s="24"/>
+      <c r="P20" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Li</v>
+      </c>
+      <c r="Q20" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆪ</v>
+      </c>
+      <c r="S20" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Li</v>
+      </c>
+      <c r="T20" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆪ</v>
+      </c>
+      <c r="U20" s="25"/>
+      <c r="V20" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Li/ㆪ》/</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="27.75" thickBot="1">
+      <c r="A21" s="19">
+        <v>52</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>650</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>547</v>
+      </c>
+      <c r="J21" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>595</v>
+      </c>
+      <c r="M21" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O21" s="24"/>
+      <c r="P21" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>Loo</v>
+      </c>
+      <c r="Q21" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆧ</v>
+      </c>
+      <c r="S21" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Loo</v>
+      </c>
+      <c r="T21" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆧ</v>
+      </c>
+      <c r="U21" s="25"/>
+      <c r="V21" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》Loo/ㆧ》/</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A22" s="19">
+        <v>35</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="M22" s="19"/>
+      <c r="N22" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O22" s="24"/>
+      <c r="P22" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iang</v>
+      </c>
+      <c r="Q22" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄤ</v>
+      </c>
+      <c r="S22" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iang</v>
+      </c>
+      <c r="T22" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄤ</v>
+      </c>
+      <c r="U22" s="25"/>
+      <c r="V22" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iang/ㄧㄤ》/</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A23" s="19">
+        <v>41</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="M23" s="19"/>
+      <c r="N23" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O23" s="24"/>
+      <c r="P23" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iauh</v>
+      </c>
+      <c r="Q23" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄠㆷ</v>
+      </c>
+      <c r="S23" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iauh</v>
+      </c>
+      <c r="T23" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄠㆷ</v>
+      </c>
+      <c r="U23" s="25"/>
+      <c r="V23" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iauh/ㄧㄠㆷ》/</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A24" s="19">
+        <v>45</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>597</v>
+      </c>
+      <c r="M24" s="19"/>
+      <c r="N24" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O24" s="24"/>
+      <c r="P24" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iong</v>
+      </c>
+      <c r="Q24" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆲ</v>
+      </c>
+      <c r="S24" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iong</v>
+      </c>
+      <c r="T24" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆲ</v>
+      </c>
+      <c r="U24" s="25"/>
+      <c r="V24" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iong/ㄧㆲ》/</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A25" s="19">
+        <v>68</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="M25" s="19"/>
+      <c r="N25" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O25" s="24"/>
+      <c r="P25" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>uang</v>
+      </c>
+      <c r="Q25" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㄤ</v>
+      </c>
+      <c r="S25" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>uang</v>
+      </c>
+      <c r="T25" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㄤ</v>
+      </c>
+      <c r="U25" s="25"/>
+      <c r="V25" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uang/ㄨㄤ》/</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A26" s="19">
+        <v>72</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>598</v>
+      </c>
+      <c r="M26" s="19"/>
+      <c r="N26" s="23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O26" s="24"/>
+      <c r="P26" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>uaih</v>
+      </c>
+      <c r="Q26" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㄞㆷ</v>
+      </c>
+      <c r="S26" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>uaih</v>
+      </c>
+      <c r="T26" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㄞㆷ</v>
+      </c>
+      <c r="U26" s="25"/>
+      <c r="V26" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uaih/ㄨㄞㆷ》/</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A27" s="19">
+        <v>78</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="I27" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="K27" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="L27" s="54" t="s">
+        <v>577</v>
+      </c>
+      <c r="M27" s="29"/>
+      <c r="N27" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O27" s="24"/>
+      <c r="P27" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>uih</v>
+      </c>
+      <c r="Q27" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㄧㆷ</v>
+      </c>
+      <c r="S27" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>uih</v>
+      </c>
+      <c r="T27" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㄧㆷ</v>
+      </c>
+      <c r="U27" s="25"/>
+      <c r="V27" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uih/ㄨㄧㆷ》/</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A28" s="19">
+        <v>7</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="19"/>
+      <c r="N28" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O28" s="24"/>
+      <c r="P28" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ang</v>
+      </c>
+      <c r="Q28" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄤ</v>
+      </c>
+      <c r="S28" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ang</v>
+      </c>
+      <c r="T28" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄤ</v>
+      </c>
+      <c r="U28" s="25"/>
+      <c r="V28" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ang/ㄤ》/</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A29" s="19">
+        <v>13</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="L29" s="54" t="s">
+        <v>578</v>
+      </c>
+      <c r="M29" s="19"/>
+      <c r="N29" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O29" s="24"/>
+      <c r="P29" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>aih</v>
+      </c>
+      <c r="Q29" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄞㆷ</v>
+      </c>
+      <c r="S29" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>aih</v>
+      </c>
+      <c r="T29" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄞㆷ</v>
+      </c>
+      <c r="U29" s="25"/>
+      <c r="V29" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》aih/ㄞㆷ》/</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A30" s="19">
+        <v>15</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="J30" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="M30" s="19"/>
+      <c r="N30" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O30" s="24"/>
+      <c r="P30" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>auh</v>
+      </c>
+      <c r="Q30" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄠㆷ</v>
+      </c>
+      <c r="S30" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>auh</v>
+      </c>
+      <c r="T30" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄠㆷ</v>
+      </c>
+      <c r="U30" s="25"/>
+      <c r="V30" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》auh/ㄠㆷ》/</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A31" s="19">
+        <v>25</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="M31" s="19"/>
+      <c r="N31" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O31" s="24"/>
+      <c r="P31" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ing</v>
+      </c>
+      <c r="Q31" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄥ</v>
+      </c>
+      <c r="S31" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ing</v>
+      </c>
+      <c r="T31" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄥ</v>
+      </c>
+      <c r="U31" s="25"/>
+      <c r="V31" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ing/ㄧㄥ》/</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A32" s="19">
+        <v>31</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="J32" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="M32" s="19"/>
+      <c r="N32" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O32" s="24"/>
+      <c r="P32" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iah</v>
+      </c>
+      <c r="Q32" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄚㆷ</v>
+      </c>
+      <c r="S32" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iah</v>
+      </c>
+      <c r="T32" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄚㆷ</v>
+      </c>
+      <c r="U32" s="25"/>
+      <c r="V32" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iah/ㄧㄚㆷ》/</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A33" s="19">
+        <v>33</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="J33" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>601</v>
+      </c>
+      <c r="M33" s="19"/>
+      <c r="N33" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O33" s="24"/>
+      <c r="P33" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iam</v>
+      </c>
+      <c r="Q33" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆰ</v>
+      </c>
+      <c r="S33" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iam</v>
+      </c>
+      <c r="T33" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆰ</v>
+      </c>
+      <c r="U33" s="25"/>
+      <c r="V33" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iam/ㄧㆰ》/</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A34" s="19">
+        <v>34</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="J34" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="M34" s="19"/>
+      <c r="N34" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O34" s="24"/>
+      <c r="P34" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ian</v>
+      </c>
+      <c r="Q34" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄢ</v>
+      </c>
+      <c r="S34" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ian</v>
+      </c>
+      <c r="T34" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄢ</v>
+      </c>
+      <c r="U34" s="25"/>
+      <c r="V34" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ian/ㄧㄢ》/</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A35" s="19">
+        <v>36</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="J35" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="M35" s="19"/>
+      <c r="N35" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O35" s="24"/>
+      <c r="P35" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iap</v>
+      </c>
+      <c r="Q35" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄚㆴ</v>
+      </c>
+      <c r="S35" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iap</v>
+      </c>
+      <c r="T35" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄚㆴ</v>
+      </c>
+      <c r="U35" s="25"/>
+      <c r="V35" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iap/ㄧㄚㆴ》/</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A36" s="19">
+        <v>37</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="J36" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="M36" s="19"/>
+      <c r="N36" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O36" s="24"/>
+      <c r="P36" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iat</v>
+      </c>
+      <c r="Q36" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄚㆵ</v>
+      </c>
+      <c r="S36" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iat</v>
+      </c>
+      <c r="T36" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄚㆵ</v>
+      </c>
+      <c r="U36" s="25"/>
+      <c r="V36" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iat/ㄧㄚㆵ》/</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A37" s="19">
+        <v>38</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="J37" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="M37" s="19"/>
+      <c r="N37" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O37" s="24"/>
+      <c r="P37" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iak</v>
+      </c>
+      <c r="Q37" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄚㆻ</v>
+      </c>
+      <c r="S37" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iak</v>
+      </c>
+      <c r="T37" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄚㆻ</v>
+      </c>
+      <c r="U37" s="25"/>
+      <c r="V37" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iak/ㄧㄚㆻ》/</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A38" s="19">
+        <v>39</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="I38" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="M38" s="19"/>
+      <c r="N38" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O38" s="24"/>
+      <c r="P38" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iau</v>
+      </c>
+      <c r="Q38" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄠ</v>
+      </c>
+      <c r="S38" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iau</v>
+      </c>
+      <c r="T38" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄠ</v>
+      </c>
+      <c r="U38" s="25"/>
+      <c r="V38" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iau/ㄧㄠ》/</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A39" s="19">
+        <v>44</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="I39" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="J39" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>605</v>
+      </c>
+      <c r="M39" s="19"/>
+      <c r="N39" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O39" s="24"/>
+      <c r="P39" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iorh</v>
+      </c>
+      <c r="Q39" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄜㆷ</v>
+      </c>
+      <c r="S39" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iorh</v>
+      </c>
+      <c r="T39" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄜㆷ</v>
+      </c>
+      <c r="U39" s="25"/>
+      <c r="V39" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iorh/ㄧㄜㆷ》/</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A40" s="19">
+        <v>46</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="I40" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="J40" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="M40" s="19"/>
+      <c r="N40" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O40" s="24"/>
+      <c r="P40" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iook</v>
+      </c>
+      <c r="Q40" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆦㆻ</v>
+      </c>
+      <c r="S40" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iook</v>
+      </c>
+      <c r="T40" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆦㆻ</v>
+      </c>
+      <c r="U40" s="25"/>
+      <c r="V40" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iook/ㄧㆦㆻ》/</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A41" s="19">
+        <v>54</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="F41" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="G41" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="H41" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="I41" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="J41" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="K41" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="L41" s="55" t="s">
+        <v>580</v>
+      </c>
+      <c r="M41" s="19"/>
+      <c r="N41" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O41" s="24"/>
+      <c r="P41" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ooh</v>
+      </c>
+      <c r="Q41" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆦㆷ</v>
+      </c>
+      <c r="S41" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ooh</v>
+      </c>
+      <c r="T41" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆦㆷ</v>
+      </c>
+      <c r="U41" s="25"/>
+      <c r="V41" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ooh/ㆦㆷ》/</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A42" s="19">
+        <v>57</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="I42" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="J42" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="M42" s="19"/>
+      <c r="N42" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O42" s="24"/>
+      <c r="P42" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ong</v>
+      </c>
+      <c r="Q42" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆲ</v>
+      </c>
+      <c r="S42" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ong</v>
+      </c>
+      <c r="T42" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆲ</v>
+      </c>
+      <c r="U42" s="25"/>
+      <c r="V42" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ong/ㆲ》/</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A43" s="19">
+        <v>66</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="I43" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="M43" s="19"/>
+      <c r="N43" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O43" s="24"/>
+      <c r="P43" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>uah</v>
+      </c>
+      <c r="Q43" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㄚㆷ</v>
+      </c>
+      <c r="S43" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>uah</v>
+      </c>
+      <c r="T43" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㄚㆷ</v>
+      </c>
+      <c r="U43" s="25"/>
+      <c r="V43" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uah/ㄨㄚㆷ》/</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A44" s="19">
+        <v>67</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="I44" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="J44" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="M44" s="19"/>
+      <c r="N44" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O44" s="24"/>
+      <c r="P44" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>uan</v>
+      </c>
+      <c r="Q44" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㄢ</v>
+      </c>
+      <c r="S44" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>uan</v>
+      </c>
+      <c r="T44" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㄢ</v>
+      </c>
+      <c r="U44" s="25"/>
+      <c r="V44" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uan/ㄨㄢ》/</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A45" s="19">
+        <v>69</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>338</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="I45" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="J45" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="L45" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="M45" s="19"/>
+      <c r="N45" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O45" s="24"/>
+      <c r="P45" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>uat</v>
+      </c>
+      <c r="Q45" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㄚㆵ</v>
+      </c>
+      <c r="S45" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>uat</v>
+      </c>
+      <c r="T45" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㄚㆵ</v>
+      </c>
+      <c r="U45" s="25"/>
+      <c r="V45" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uat/ㄨㄚㆵ》/</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A46" s="19">
+        <v>70</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="I46" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="J46" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="L46" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="M46" s="19"/>
+      <c r="N46" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O46" s="24"/>
+      <c r="P46" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>uai</v>
+      </c>
+      <c r="Q46" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㄞ</v>
+      </c>
+      <c r="S46" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>uai</v>
+      </c>
+      <c r="T46" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㄞ</v>
+      </c>
+      <c r="U46" s="25"/>
+      <c r="V46" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》uai/ㄨㄞ》/</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A47" s="19">
+        <v>75</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="I47" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="J47" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="L47" s="19" t="s">
+        <v>609</v>
+      </c>
+      <c r="M47" s="19"/>
+      <c r="N47" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O47" s="24"/>
+      <c r="P47" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ueh</v>
+      </c>
+      <c r="Q47" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄨㆤㆷ</v>
+      </c>
+      <c r="S47" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ueh</v>
+      </c>
+      <c r="T47" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄨㆤㆷ</v>
+      </c>
+      <c r="U47" s="25"/>
+      <c r="V47" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ueh/ㄨㆤㆷ》/</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A48" s="19">
+        <v>82</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="H48" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="I48" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="J48" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="K48" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="L48" s="55" t="s">
+        <v>581</v>
+      </c>
+      <c r="M48" s="19"/>
+      <c r="N48" s="23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O48" s="24"/>
+      <c r="P48" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ngh</v>
+      </c>
+      <c r="Q48" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆭㆷ</v>
+      </c>
+      <c r="S48" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ngh</v>
+      </c>
+      <c r="T48" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆭㆷ</v>
+      </c>
+      <c r="U48" s="25"/>
+      <c r="V48" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ngh/ㆭㆷ》/</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A49" s="19">
+        <v>3</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="K49" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L49" s="19" t="s">
+        <v>610</v>
+      </c>
+      <c r="M49" s="19"/>
+      <c r="N49" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O49" s="24"/>
+      <c r="P49" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ah</v>
+      </c>
+      <c r="Q49" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄚㆷ</v>
+      </c>
+      <c r="S49" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ah</v>
+      </c>
+      <c r="T49" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄚㆷ</v>
+      </c>
+      <c r="U49" s="25"/>
+      <c r="V49" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ah/ㄚㆷ》/</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A50" s="19">
+        <v>5</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="J50" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="M50" s="19"/>
+      <c r="N50" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O50" s="24"/>
+      <c r="P50" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>am</v>
+      </c>
+      <c r="Q50" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆰ</v>
+      </c>
+      <c r="S50" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>am</v>
+      </c>
+      <c r="T50" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆰ</v>
+      </c>
+      <c r="U50" s="25"/>
+      <c r="V50" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》am/ㆰ》/</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A51" s="19">
+        <v>6</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I51" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="M51" s="19"/>
+      <c r="N51" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O51" s="24"/>
+      <c r="P51" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>an</v>
+      </c>
+      <c r="Q51" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄢ</v>
+      </c>
+      <c r="S51" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>an</v>
+      </c>
+      <c r="T51" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄢ</v>
+      </c>
+      <c r="U51" s="25"/>
+      <c r="V51" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》an/ㄢ》/</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A52" s="19">
+        <v>8</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I52" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J52" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="K52" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="L52" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="M52" s="19"/>
+      <c r="N52" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O52" s="24"/>
+      <c r="P52" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ap</v>
+      </c>
+      <c r="Q52" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄚㆴ</v>
+      </c>
+      <c r="S52" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ap</v>
+      </c>
+      <c r="T52" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄚㆴ</v>
+      </c>
+      <c r="U52" s="25"/>
+      <c r="V52" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ap/ㄚㆴ》/</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A53" s="19">
+        <v>9</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G53" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="I53" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="J53" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="K53" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="L53" s="19" t="s">
+        <v>613</v>
+      </c>
+      <c r="M53" s="19"/>
+      <c r="N53" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O53" s="24"/>
+      <c r="P53" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>at</v>
+      </c>
+      <c r="Q53" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄚㆵ</v>
+      </c>
+      <c r="S53" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>at</v>
+      </c>
+      <c r="T53" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄚㆵ</v>
+      </c>
+      <c r="U53" s="25"/>
+      <c r="V53" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》at/ㄚㆵ》/</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A54" s="19">
+        <v>10</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="I54" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="J54" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="L54" s="19" t="s">
+        <v>614</v>
+      </c>
+      <c r="M54" s="19"/>
+      <c r="N54" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O54" s="24"/>
+      <c r="P54" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ak</v>
+      </c>
+      <c r="Q54" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄚㆻ</v>
+      </c>
+      <c r="S54" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ak</v>
+      </c>
+      <c r="T54" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄚㆻ</v>
+      </c>
+      <c r="U54" s="25"/>
+      <c r="V54" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ak/ㄚㆻ》/</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A55" s="19">
+        <v>11</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="I55" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="L55" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M55" s="19"/>
+      <c r="N55" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O55" s="24"/>
+      <c r="P55" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ai</v>
+      </c>
+      <c r="Q55" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄞ</v>
+      </c>
+      <c r="S55" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ai</v>
+      </c>
+      <c r="T55" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄞ</v>
+      </c>
+      <c r="U55" s="25"/>
+      <c r="V55" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ai/ㄞ》/</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A56" s="19">
+        <v>14</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H56" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I56" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="J56" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="K56" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L56" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="M56" s="19"/>
+      <c r="N56" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O56" s="24"/>
+      <c r="P56" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>au</v>
+      </c>
+      <c r="Q56" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄠ</v>
+      </c>
+      <c r="S56" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>au</v>
+      </c>
+      <c r="T56" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄠ</v>
+      </c>
+      <c r="U56" s="25"/>
+      <c r="V56" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》au/ㄠ》/</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A57" s="19">
+        <v>18</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I57" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="J57" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="L57" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="M57" s="19"/>
+      <c r="N57" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O57" s="24"/>
+      <c r="P57" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>eh</v>
+      </c>
+      <c r="Q57" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆤㆷ</v>
+      </c>
+      <c r="S57" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>eh</v>
+      </c>
+      <c r="T57" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆤㆷ</v>
+      </c>
+      <c r="U57" s="25"/>
+      <c r="V57" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》eh/ㆤㆷ》/</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A58" s="19">
+        <v>22</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="I58" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="J58" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="L58" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="M58" s="19"/>
+      <c r="N58" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O58" s="24"/>
+      <c r="P58" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ih</v>
+      </c>
+      <c r="Q58" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆷ</v>
+      </c>
+      <c r="S58" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ih</v>
+      </c>
+      <c r="T58" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆷ</v>
+      </c>
+      <c r="U58" s="25"/>
+      <c r="V58" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ih/ㄧㆷ》/</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A59" s="19">
+        <v>23</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="I59" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="J59" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="K59" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L59" s="19" t="s">
+        <v>617</v>
+      </c>
+      <c r="M59" s="19"/>
+      <c r="N59" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O59" s="24"/>
+      <c r="P59" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>im</v>
+      </c>
+      <c r="Q59" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆬ</v>
+      </c>
+      <c r="S59" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>im</v>
+      </c>
+      <c r="T59" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆬ</v>
+      </c>
+      <c r="U59" s="25"/>
+      <c r="V59" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》im/ㄧㆬ》/</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A60" s="19">
+        <v>24</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="H60" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I60" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J60" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="L60" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="M60" s="19"/>
+      <c r="N60" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O60" s="24"/>
+      <c r="P60" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>in</v>
+      </c>
+      <c r="Q60" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄣ</v>
+      </c>
+      <c r="S60" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>in</v>
+      </c>
+      <c r="T60" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄣ</v>
+      </c>
+      <c r="U60" s="25"/>
+      <c r="V60" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》in/ㄧㄣ》/</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A61" s="19">
+        <v>26</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="H61" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="I61" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="J61" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L61" s="19" t="s">
+        <v>618</v>
+      </c>
+      <c r="M61" s="19"/>
+      <c r="N61" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O61" s="24"/>
+      <c r="P61" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ip</v>
+      </c>
+      <c r="Q61" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>一ㆴ</v>
+      </c>
+      <c r="S61" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ip</v>
+      </c>
+      <c r="T61" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>一ㆴ</v>
+      </c>
+      <c r="U61" s="25"/>
+      <c r="V61" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ip/一ㆴ》/</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A62" s="19">
+        <v>27</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="J62" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="L62" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="M62" s="19"/>
+      <c r="N62" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O62" s="24"/>
+      <c r="P62" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>it</v>
+      </c>
+      <c r="Q62" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆵ</v>
+      </c>
+      <c r="S62" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>it</v>
+      </c>
+      <c r="T62" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆵ</v>
+      </c>
+      <c r="U62" s="25"/>
+      <c r="V62" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》it/ㄧㆵ》/</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="27.75" thickBot="1">
+      <c r="A63" s="19">
+        <v>28</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="I63" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="J63" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="K63" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="L63" s="19" t="s">
+        <v>620</v>
+      </c>
+      <c r="M63" s="19"/>
+      <c r="N63" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O63" s="24"/>
+      <c r="P63" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iek</v>
+      </c>
+      <c r="Q63" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㆻ</v>
+      </c>
+      <c r="S63" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iek</v>
+      </c>
+      <c r="T63" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㆻ</v>
+      </c>
+      <c r="U63" s="25"/>
+      <c r="V63" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iek/ㄧㆻ》/</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A64" s="19">
+        <v>29</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="I64" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="J64" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L64" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="M64" s="19"/>
+      <c r="N64" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O64" s="24"/>
+      <c r="P64" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ia</v>
+      </c>
+      <c r="Q64" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄚ</v>
+      </c>
+      <c r="S64" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ia</v>
+      </c>
+      <c r="T64" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄚ</v>
+      </c>
+      <c r="U64" s="25"/>
+      <c r="V64" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ia/ㄧㄚ》/</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A65" s="19">
+        <v>42</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="I65" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="J65" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="K65" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="L65" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="M65" s="19"/>
+      <c r="N65" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O65" s="24"/>
+      <c r="P65" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>ior</v>
+      </c>
+      <c r="Q65" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄜ</v>
+      </c>
+      <c r="S65" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>ior</v>
+      </c>
+      <c r="T65" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄜ</v>
+      </c>
+      <c r="U65" s="25"/>
+      <c r="V65" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》ior/ㄧㄜ》/</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A66" s="19">
+        <v>47</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="H66" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J66" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="K66" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="L66" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="M66" s="19"/>
+      <c r="N66" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O66" s="24"/>
+      <c r="P66" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>iu</v>
+      </c>
+      <c r="Q66" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㄧㄨ</v>
+      </c>
+      <c r="S66" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>iu</v>
+      </c>
+      <c r="T66" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄧㄨ</v>
+      </c>
+      <c r="U66" s="25"/>
+      <c r="V66" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》iu/ㄧㄨ》/</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A67" s="19">
+        <v>51</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="H67" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="I67" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="J67" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="L67" s="19" t="s">
+        <v>621</v>
+      </c>
+      <c r="M67" s="19"/>
+      <c r="N67" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O67" s="24"/>
+      <c r="P67" s="51" t="str">
+        <f t="shared" si="1"/>
+        <v>oo</v>
+      </c>
+      <c r="Q67" s="51" t="str">
+        <f t="shared" si="2"/>
+        <v>ㆦ</v>
+      </c>
+      <c r="S67" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>oo</v>
+      </c>
+      <c r="T67" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㆦ</v>
+      </c>
+      <c r="U67" s="25"/>
+      <c r="V67" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》oo/ㆦ》/</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A68" s="19">
+        <v>53</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="G68" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="H68" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="I68" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="J68" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="K68" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="L68" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="M68" s="19"/>
+      <c r="N68" s="23">
+        <f t="shared" ref="N68:N85" si="11" xml:space="preserve"> LEN(C68)</f>
+        <v>2</v>
+      </c>
+      <c r="O68" s="24"/>
+      <c r="P68" s="51" t="str">
+        <f t="shared" ref="P68:P85" si="12">G68</f>
+        <v>orh</v>
+      </c>
+      <c r="Q68" s="51" t="str">
+        <f t="shared" ref="Q68:Q85" si="13">K68</f>
+        <v>ㄜㆷ</v>
+      </c>
+      <c r="S68" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>orh</v>
+      </c>
+      <c r="T68" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>ㄜㆷ</v>
+      </c>
+      <c r="U68" s="25"/>
+      <c r="V68" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">    - xform/》orh/ㄜㆷ》/</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A69" s="19">
+        <v>56</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G69" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="H69" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="I69" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="J69" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="K69" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="L69" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="M69" s="19"/>
+      <c r="N69" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O69" s="24"/>
+      <c r="P69" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>oom</v>
+      </c>
+      <c r="Q69" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㆱ</v>
+      </c>
+      <c r="S69" s="3" t="str">
+        <f t="shared" ref="S69:S85" si="14" xml:space="preserve"> _xlfn.CONCAT(P69)</f>
+        <v>oom</v>
+      </c>
+      <c r="T69" s="3" t="str">
+        <f t="shared" ref="T69:T85" si="15" xml:space="preserve"> IFERROR( _xlfn.CONCAT(Q69, ""), "" )</f>
+        <v>ㆱ</v>
+      </c>
+      <c r="U69" s="25"/>
+      <c r="V69" s="26" t="str">
+        <f t="shared" ref="V69:V85" si="16" xml:space="preserve"> IF(AND(Q69&lt;&gt;"", P69&lt;&gt;""), "    - xform/》" &amp; S69 &amp;  "/"  &amp; T69 &amp;  "》/", "")</f>
+        <v xml:space="preserve">    - xform/》oom/ㆱ》/</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A70" s="19">
+        <v>58</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G70" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="H70" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="I70" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="J70" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="K70" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="L70" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="M70" s="19"/>
+      <c r="N70" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O70" s="24"/>
+      <c r="P70" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>oop</v>
+      </c>
+      <c r="Q70" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㆦㆴ</v>
+      </c>
+      <c r="S70" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>oop</v>
+      </c>
+      <c r="T70" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㆦㆴ</v>
+      </c>
+      <c r="U70" s="25"/>
+      <c r="V70" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》oop/ㆦㆴ》/</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A71" s="19">
+        <v>59</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="G71" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="H71" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="I71" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="J71" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="K71" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="L71" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="M71" s="19"/>
+      <c r="N71" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O71" s="24"/>
+      <c r="P71" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>ok</v>
+      </c>
+      <c r="Q71" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㆦㆻ</v>
+      </c>
+      <c r="S71" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>ok</v>
+      </c>
+      <c r="T71" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㆦㆻ</v>
+      </c>
+      <c r="U71" s="25"/>
+      <c r="V71" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》ok/ㆦㆻ》/</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A72" s="19">
+        <v>61</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="G72" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="H72" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="I72" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="J72" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="K72" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="L72" s="19" t="s">
+        <v>626</v>
+      </c>
+      <c r="M72" s="19"/>
+      <c r="N72" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O72" s="24"/>
+      <c r="P72" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>uh</v>
+      </c>
+      <c r="Q72" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄨㆷ</v>
+      </c>
+      <c r="S72" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>uh</v>
+      </c>
+      <c r="T72" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄨㆷ</v>
+      </c>
+      <c r="U72" s="25"/>
+      <c r="V72" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》uh/ㄨㆷ》/</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A73" s="19">
+        <v>62</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="H73" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="I73" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="J73" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="L73" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="M73" s="19"/>
+      <c r="N73" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O73" s="24"/>
+      <c r="P73" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>un</v>
+      </c>
+      <c r="Q73" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄨㄣ</v>
+      </c>
+      <c r="S73" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>un</v>
+      </c>
+      <c r="T73" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄨㄣ</v>
+      </c>
+      <c r="U73" s="25"/>
+      <c r="V73" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》un/ㄨㄣ》/</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A74" s="19">
+        <v>63</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G74" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H74" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="I74" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="J74" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="K74" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="L74" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="M74" s="19"/>
+      <c r="N74" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O74" s="24"/>
+      <c r="P74" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>ut</v>
+      </c>
+      <c r="Q74" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄨㆵ</v>
+      </c>
+      <c r="S74" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>ut</v>
+      </c>
+      <c r="T74" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄨㆵ</v>
+      </c>
+      <c r="U74" s="25"/>
+      <c r="V74" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》ut/ㄨㆵ》/</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A75" s="19">
+        <v>64</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="G75" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="H75" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="I75" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="J75" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="K75" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="L75" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="M75" s="19"/>
+      <c r="N75" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O75" s="24"/>
+      <c r="P75" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>ua</v>
+      </c>
+      <c r="Q75" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄨㄚ</v>
+      </c>
+      <c r="S75" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>ua</v>
+      </c>
+      <c r="T75" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄨㄚ</v>
+      </c>
+      <c r="U75" s="25"/>
+      <c r="V75" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》ua/ㄨㄚ》/</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A76" s="19">
+        <v>74</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="G76" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="H76" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="I76" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="J76" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="K76" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="L76" s="19" t="s">
+        <v>628</v>
+      </c>
+      <c r="M76" s="19"/>
+      <c r="N76" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O76" s="24"/>
+      <c r="P76" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>ue</v>
+      </c>
+      <c r="Q76" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄨㆤ</v>
+      </c>
+      <c r="S76" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>ue</v>
+      </c>
+      <c r="T76" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄨㆤ</v>
+      </c>
+      <c r="U76" s="25"/>
+      <c r="V76" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》ue/ㄨㆤ》/</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A77" s="19">
+        <v>76</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="H77" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="I77" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="J77" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="K77" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="L77" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="M77" s="19"/>
+      <c r="N77" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O77" s="24"/>
+      <c r="P77" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>ui</v>
+      </c>
+      <c r="Q77" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄨㄧ</v>
+      </c>
+      <c r="S77" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>ui</v>
+      </c>
+      <c r="T77" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄨㄧ</v>
+      </c>
+      <c r="U77" s="25"/>
+      <c r="V77" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》ui/ㄨㄧ》/</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A78" s="19">
+        <v>80</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="E78" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="F78" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="G78" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="H78" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="I78" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="J78" s="35" t="s">
+        <v>392</v>
+      </c>
+      <c r="K78" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="L78" s="54" t="s">
+        <v>582</v>
+      </c>
+      <c r="M78" s="19"/>
+      <c r="N78" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O78" s="24"/>
+      <c r="P78" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>mh</v>
+      </c>
+      <c r="Q78" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㆬㆷ</v>
+      </c>
+      <c r="S78" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>mh</v>
+      </c>
+      <c r="T78" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㆬㆷ</v>
+      </c>
+      <c r="U78" s="25"/>
+      <c r="V78" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》mh/ㆬㆷ》/</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A79" s="19">
+        <v>81</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="G79" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="H79" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="I79" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="J79" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="K79" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="L79" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="M79" s="19"/>
+      <c r="N79" s="23">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O79" s="24"/>
+      <c r="P79" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>ng</v>
+      </c>
+      <c r="Q79" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㆭ</v>
+      </c>
+      <c r="S79" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>ng</v>
+      </c>
+      <c r="T79" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㆭ</v>
+      </c>
+      <c r="U79" s="25"/>
+      <c r="V79" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》ng/ㆭ》/</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A80" s="19">
+        <v>1</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I80" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="K80" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="M80" s="19"/>
+      <c r="N80" s="23">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O80" s="24"/>
+      <c r="P80" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>a</v>
+      </c>
+      <c r="Q80" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄚ</v>
+      </c>
+      <c r="S80" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>a</v>
+      </c>
+      <c r="T80" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄚ</v>
+      </c>
+      <c r="U80" s="25"/>
+      <c r="V80" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》a/ㄚ》/</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A81" s="19">
+        <v>16</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="G81" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H81" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="I81" s="22">
+        <v>0</v>
+      </c>
+      <c r="J81" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="K81" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="L81" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="M81" s="19"/>
+      <c r="N81" s="23">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O81" s="24"/>
+      <c r="P81" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>e</v>
+      </c>
+      <c r="Q81" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㆤ</v>
+      </c>
+      <c r="S81" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>e</v>
+      </c>
+      <c r="T81" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㆤ</v>
+      </c>
+      <c r="U81" s="25"/>
+      <c r="V81" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》e/ㆤ》/</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A82" s="19">
+        <v>20</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="G82" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="H82" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="I82" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="J82" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="K82" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="L82" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="M82" s="19"/>
+      <c r="N82" s="23">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O82" s="24"/>
+      <c r="P82" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>i</v>
+      </c>
+      <c r="Q82" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄧ</v>
+      </c>
+      <c r="S82" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>i</v>
+      </c>
+      <c r="T82" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄧ</v>
+      </c>
+      <c r="U82" s="25"/>
+      <c r="V82" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》i/ㄧ》/</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A83" s="19">
+        <v>50</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G83" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H83" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="I83" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="J83" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="K83" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="L83" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="M83" s="19"/>
+      <c r="N83" s="23">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O83" s="24"/>
+      <c r="P83" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>or</v>
+      </c>
+      <c r="Q83" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄜ</v>
+      </c>
+      <c r="S83" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>or</v>
+      </c>
+      <c r="T83" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄜ</v>
+      </c>
+      <c r="U83" s="25"/>
+      <c r="V83" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》or/ㄜ》/</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A84" s="19">
+        <v>60</v>
+      </c>
+      <c r="B84" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="G84" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="H84" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="I84" s="22" t="s">
+        <v>300</v>
+      </c>
+      <c r="J84" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="K84" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="L84" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="M84" s="19"/>
+      <c r="N84" s="23">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O84" s="24"/>
+      <c r="P84" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>u</v>
+      </c>
+      <c r="Q84" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㄨ</v>
+      </c>
+      <c r="S84" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>u</v>
+      </c>
+      <c r="T84" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㄨ</v>
+      </c>
+      <c r="U84" s="25"/>
+      <c r="V84" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》u/ㄨ》/</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A85" s="19">
+        <v>79</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="G85" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="H85" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="I85" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="J85" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="K85" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="L85" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="M85" s="19"/>
+      <c r="N85" s="23">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O85" s="24"/>
+      <c r="P85" s="51" t="str">
+        <f t="shared" si="12"/>
+        <v>m</v>
+      </c>
+      <c r="Q85" s="51" t="str">
+        <f t="shared" si="13"/>
+        <v>ㆬ</v>
+      </c>
+      <c r="S85" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>m</v>
+      </c>
+      <c r="T85" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>ㆬ</v>
+      </c>
+      <c r="U85" s="25"/>
+      <c r="V85" s="26" t="str">
+        <f t="shared" si="16"/>
+        <v xml:space="preserve">    - xform/》m/ㆬ》/</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" ht="27" thickBot="1"/>
+    <row r="87" spans="1:22" ht="48.75" thickBot="1">
+      <c r="B87" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" ht="27.75" thickBot="1">
+      <c r="B88" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="C88" s="19">
+        <f xml:space="preserve"> HEX2DEC(VALUE(RIGHT(B88,4)))</f>
+        <v>771</v>
+      </c>
+      <c r="D88" s="19"/>
+      <c r="E88" s="19" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(B88,4))))</f>
+        <v>ã</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" ht="27.75" thickBot="1">
+      <c r="B89" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="C89" s="19">
+        <f xml:space="preserve"> HEX2DEC(VALUE(RIGHT(B89,4)))</f>
+        <v>660</v>
+      </c>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(B89,4))))</f>
+        <v>aʔ</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" ht="27" thickBot="1"/>
+    <row r="91" spans="1:22" ht="27" thickBot="1">
+      <c r="B91" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C91" s="11">
+        <f xml:space="preserve"> HEX2DEC(VALUE(RIGHT(B91,4)))</f>
+        <v>2134</v>
+      </c>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("o", _xlfn.UNICHAR( RIGHT(B91,4)))</f>
+        <v>o͘</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" ht="27" thickBot="1">
+      <c r="B92" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="C92" s="11">
+        <f xml:space="preserve"> _xlfn.UNICODE( RIGHT(B92,1) )</f>
+        <v>856</v>
+      </c>
+      <c r="D92" s="11"/>
+      <c r="E92" s="11" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("o", _xlfn.UNICHAR(C92))</f>
+        <v>o͘</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" ht="27" thickBot="1"/>
+    <row r="94" spans="1:22" ht="27" thickBot="1">
+      <c r="B94" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="D94" s="50"/>
+    </row>
+    <row r="95" spans="1:22" ht="27" thickBot="1">
+      <c r="B95" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="D95" s="50"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="str">
+        <f xml:space="preserve"> "(""" &amp; _xlfn.TEXTJOIN(""",""",TRUE,H4:H85) &amp; """)"</f>
+        <v>("uainnh","iannh","niao","niuh","nuai","nah","nai","ennh","nia","nioo","niu","niuh","nua","nui","na","ne","ni","noo","iang","iaoh","iong","uang","uaih","uih","ang","aih","aoh","ing","iah","iam","ian","iap","iat","iak","iao","ioh","iok","ooh","ong","uah","uan","uat","uai","ueh","ngh","ah","am","an","ap","at","ak","ai","ao","eh","ih","im","in","ip","it","ik","ia","io","iu","oo","oh","om","op","ok","uh","un","ut","ua","ue","ui","mh","ng","a","e","i","o","u","m")</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C4C1DF-73FB-4190-AA45-450864391596}">
   <dimension ref="A1:L97"/>
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1"/>
@@ -18055,7 +24359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19903CB1-FE24-40F3-8044-C24D05C4630C}">
   <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="25.5" outlineLevelCol="1"/>
@@ -19880,7 +26184,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12E1B17D-6C8E-4FC8-90DB-8E26E275724A}">
   <dimension ref="A1:AC28"/>
   <sheetFormatPr defaultRowHeight="25.5"/>
@@ -21380,7 +27684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388995E4-95A2-4238-8BF9-FE169D8A4AC0}">
   <dimension ref="A1:AU97"/>
   <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
@@ -27442,7 +33746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B6A0F78-8639-4D67-AE59-1AEE7777B37C}">
   <dimension ref="A1:AU97"/>
   <sheetFormatPr defaultRowHeight="26.25" outlineLevelCol="1"/>
